--- a/语文群_20260914.xlsx
+++ b/语文群_20260914.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luhui\Python\checkin_v2\WeChatTextExport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_FE6A3523EDB5C01B1F34374349D54E03EE58E6DF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_FE6A3523EDB5C01B1F3437F4499744A3EE58E6DF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
